--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N126_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N126_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.6349756002642</v>
+        <v>4.490683535042932</v>
       </c>
       <c r="D2" t="n">
-        <v>26.98730573731311</v>
+        <v>4.38543718231338</v>
       </c>
       <c r="E2" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F2" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.9556369357169</v>
+        <v>6.492791002053997</v>
       </c>
       <c r="D3" t="n">
-        <v>39.34486458351473</v>
+        <v>6.393540494821145</v>
       </c>
       <c r="E3" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F3" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.96330772867173</v>
+        <v>7.631537505909156</v>
       </c>
       <c r="D4" t="n">
-        <v>46.77612089473465</v>
+        <v>7.601119645394381</v>
       </c>
       <c r="E4" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F4" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.6246259891605</v>
+        <v>5.464001723238582</v>
       </c>
       <c r="D5" t="n">
-        <v>33.60059523282288</v>
+        <v>5.460096725333718</v>
       </c>
       <c r="E5" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F5" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.93503419695583</v>
+        <v>1.126943057005322</v>
       </c>
       <c r="D6" t="n">
-        <v>7.118794601663006</v>
+        <v>1.156804122770239</v>
       </c>
       <c r="E6" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F6" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.81207062410972</v>
+        <v>5.006961476417829</v>
       </c>
       <c r="D7" t="n">
-        <v>31.37860950452715</v>
+        <v>5.099024044485661</v>
       </c>
       <c r="E7" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F7" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.79008654871572</v>
+        <v>6.140889064166305</v>
       </c>
       <c r="D8" t="n">
-        <v>38.20480807536116</v>
+        <v>6.208281312246189</v>
       </c>
       <c r="E8" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F8" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.96889845843929</v>
+        <v>4.219945999496385</v>
       </c>
       <c r="D9" t="n">
-        <v>25.81184692958166</v>
+        <v>4.19442512605702</v>
       </c>
       <c r="E9" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F9" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.70822885512062</v>
+        <v>4.827587188957101</v>
       </c>
       <c r="D10" t="n">
-        <v>29.01181797896332</v>
+        <v>4.714420421581539</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F10" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.05811620303112</v>
+        <v>4.559443882992557</v>
       </c>
       <c r="D11" t="n">
-        <v>27.91486811558881</v>
+        <v>4.536166068783182</v>
       </c>
       <c r="E11" t="n">
-        <v>10.06723117456749</v>
+        <v>1.635925065867218</v>
       </c>
       <c r="F11" t="n">
-        <v>10.01327842010634</v>
+        <v>1.62715774326728</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
